--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_怪物技能效果配置表_Combat_MonsterSkillEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_怪物技能效果配置表_Combat_MonsterSkillEffectConfig.xlsx
@@ -419,44 +419,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>MonsterSkillId</t>
+          <t>怪物技能ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>DisplayName</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>EffectKind</t>
+          <t>效果种类</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>EffectParams</t>
+          <t>效果参数</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）MonsterSkillId</t>
+          <t>主键</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）DisplayName</t>
+          <t>展示名</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）EffectKind</t>
+          <t>登记制；首版 MonsterSelfReviveOnDeath</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）EffectParams</t>
+          <t>DelaySeconds / ReviveHpRatio / InvincibleSeconds 等</t>
         </is>
       </c>
     </row>
